--- a/salidas/empresas/MA.xlsx
+++ b/salidas/empresas/MA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B2" t="n">
-        <v>4.063896179199219</v>
+        <v>4.063895225524902</v>
       </c>
       <c r="C2" t="n">
         <v>4.49399995803833</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B3" t="n">
-        <v>4.340610027313232</v>
+        <v>4.340609550476074</v>
       </c>
       <c r="C3" t="n">
         <v>4.800000190734863</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B4" t="n">
-        <v>4.147997379302979</v>
+        <v>4.147995948791504</v>
       </c>
       <c r="C4" t="n">
         <v>4.586999893188477</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B5" t="n">
-        <v>5.055005550384521</v>
+        <v>5.055003643035889</v>
       </c>
       <c r="C5" t="n">
         <v>5.590000152587891</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B6" t="n">
-        <v>6.36170768737793</v>
+        <v>6.361708641052246</v>
       </c>
       <c r="C6" t="n">
         <v>7.034999847412109</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B7" t="n">
-        <v>6.709490776062012</v>
+        <v>6.709490299224854</v>
       </c>
       <c r="C7" t="n">
         <v>7.409999847412109</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B8" t="n">
-        <v>9.213103294372559</v>
+        <v>9.213101387023926</v>
       </c>
       <c r="C8" t="n">
         <v>10.17500019073486</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B9" t="n">
-        <v>8.917922973632812</v>
+        <v>8.917917251586914</v>
       </c>
       <c r="C9" t="n">
         <v>9.848999977111816</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10905742645264</v>
+        <v>10.10905838012695</v>
       </c>
       <c r="C10" t="n">
         <v>11.15499973297119</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B11" t="n">
-        <v>9.713037490844727</v>
+        <v>9.713035583496094</v>
       </c>
       <c r="C11" t="n">
         <v>10.7180004119873</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B12" t="n">
-        <v>9.627846717834473</v>
+        <v>9.627848625183105</v>
       </c>
       <c r="C12" t="n">
         <v>10.62399959564209</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B14" t="n">
-        <v>13.57151508331299</v>
+        <v>13.57151317596436</v>
       </c>
       <c r="C14" t="n">
         <v>14.95499992370605</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B15" t="n">
-        <v>15.06624698638916</v>
+        <v>15.06625080108643</v>
       </c>
       <c r="C15" t="n">
         <v>16.58699989318848</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B17" t="n">
-        <v>12.44303703308105</v>
+        <v>12.44303321838379</v>
       </c>
       <c r="C17" t="n">
         <v>13.69900035858154</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44036197662354</v>
+        <v>13.44036483764648</v>
       </c>
       <c r="C18" t="n">
         <v>14.79699993133545</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B20" t="n">
-        <v>18.24295997619629</v>
+        <v>18.24296188354492</v>
       </c>
       <c r="C20" t="n">
         <v>20.06500053405762</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B21" t="n">
-        <v>19.56584739685059</v>
+        <v>19.56583786010742</v>
       </c>
       <c r="C21" t="n">
         <v>21.52000045776367</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B22" t="n">
-        <v>18.83457374572754</v>
+        <v>18.83456802368164</v>
       </c>
       <c r="C22" t="n">
         <v>20.70000076293945</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B24" t="n">
-        <v>20.28947639465332</v>
+        <v>20.28947067260742</v>
       </c>
       <c r="C24" t="n">
         <v>22.29899978637695</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B26" t="n">
-        <v>28.10212898254395</v>
+        <v>28.10213088989258</v>
       </c>
       <c r="C26" t="n">
         <v>30.86499977111816</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B27" t="n">
-        <v>24.17520904541016</v>
+        <v>24.17520332336426</v>
       </c>
       <c r="C27" t="n">
         <v>26.55200004577637</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B28" t="n">
-        <v>22.24212265014648</v>
+        <v>22.24212455749512</v>
       </c>
       <c r="C28" t="n">
         <v>24.41500091552734</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B29" t="n">
-        <v>22.09636497497559</v>
+        <v>22.09636878967285</v>
       </c>
       <c r="C29" t="n">
         <v>24.2549991607666</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B31" t="n">
-        <v>13.4791784286499</v>
+        <v>13.47917556762695</v>
       </c>
       <c r="C31" t="n">
         <v>14.7819995880127</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B32" t="n">
-        <v>13.24938774108887</v>
+        <v>13.24938869476318</v>
       </c>
       <c r="C32" t="n">
         <v>14.52999973297119</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B33" t="n">
-        <v>13.033278465271</v>
+        <v>13.03327560424805</v>
       </c>
       <c r="C33" t="n">
         <v>14.29300022125244</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B35" t="n">
-        <v>14.42354106903076</v>
+        <v>14.42354869842529</v>
       </c>
       <c r="C35" t="n">
         <v>15.80300045013428</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28605842590332</v>
+        <v>15.28605175018311</v>
       </c>
       <c r="C36" t="n">
         <v>16.74799919128418</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B37" t="n">
-        <v>16.75881004333496</v>
+        <v>16.75881195068359</v>
       </c>
       <c r="C37" t="n">
         <v>18.34499931335449</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B38" t="n">
-        <v>16.10838508605957</v>
+        <v>16.10837554931641</v>
       </c>
       <c r="C38" t="n">
         <v>17.63299942016602</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B39" t="n">
-        <v>15.2843656539917</v>
+        <v>15.28437042236328</v>
       </c>
       <c r="C39" t="n">
         <v>16.73100090026855</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B40" t="n">
-        <v>17.74186897277832</v>
+        <v>17.74187088012695</v>
       </c>
       <c r="C40" t="n">
         <v>19.40299987792969</v>
@@ -1229,11 +1241,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B41" t="n">
-        <v>18.52823829650879</v>
+        <v>18.52824211120605</v>
       </c>
       <c r="C41" t="n">
         <v>20.26300048828125</v>
@@ -1254,11 +1266,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B42" t="n">
-        <v>18.48434638977051</v>
+        <v>18.4843578338623</v>
       </c>
       <c r="C42" t="n">
         <v>20.21500015258789</v>
@@ -1279,11 +1291,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B43" t="n">
-        <v>20.04190635681152</v>
+        <v>20.04189872741699</v>
       </c>
       <c r="C43" t="n">
         <v>21.90200042724609</v>
@@ -1304,11 +1316,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B44" t="n">
-        <v>22.0404167175293</v>
+        <v>22.04041290283203</v>
       </c>
       <c r="C44" t="n">
         <v>24.08600044250488</v>
@@ -1329,11 +1341,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B45" t="n">
-        <v>23.42400360107422</v>
+        <v>23.42401313781738</v>
       </c>
       <c r="C45" t="n">
         <v>25.59799957275391</v>
@@ -1354,11 +1366,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B46" t="n">
-        <v>22.88103866577148</v>
+        <v>22.88104438781738</v>
       </c>
       <c r="C46" t="n">
         <v>24.98999977111816</v>
@@ -1379,11 +1391,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B47" t="n">
-        <v>20.54349136352539</v>
+        <v>20.54349517822266</v>
       </c>
       <c r="C47" t="n">
         <v>22.4370002746582</v>
@@ -1404,11 +1416,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B48" t="n">
-        <v>23.25644302368164</v>
+        <v>23.25643730163574</v>
       </c>
       <c r="C48" t="n">
         <v>25.39999961853027</v>
@@ -1429,11 +1441,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B49" t="n">
-        <v>22.72391128540039</v>
+        <v>22.72391510009766</v>
       </c>
       <c r="C49" t="n">
         <v>24.80400085449219</v>
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B50" t="n">
@@ -1479,11 +1491,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B51" t="n">
-        <v>18.27972602844238</v>
+        <v>18.27973365783691</v>
       </c>
       <c r="C51" t="n">
         <v>19.95299911499023</v>
@@ -1504,11 +1516,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B52" t="n">
-        <v>19.25706672668457</v>
+        <v>19.25705909729004</v>
       </c>
       <c r="C52" t="n">
         <v>21.00399971008301</v>
@@ -1529,11 +1541,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B53" t="n">
-        <v>18.18620300292969</v>
+        <v>18.18620109558105</v>
       </c>
       <c r="C53" t="n">
         <v>19.83600044250488</v>
@@ -1554,11 +1566,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B54" t="n">
-        <v>20.53695869445801</v>
+        <v>20.53695297241211</v>
       </c>
       <c r="C54" t="n">
         <v>22.39999961853027</v>
@@ -1579,11 +1591,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B55" t="n">
-        <v>22.02417182922363</v>
+        <v>22.02417373657227</v>
       </c>
       <c r="C55" t="n">
         <v>24.00600051879883</v>
@@ -1604,11 +1616,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B56" t="n">
-        <v>21.74619102478027</v>
+        <v>21.74618721008301</v>
       </c>
       <c r="C56" t="n">
         <v>23.70299911499023</v>
@@ -1629,7 +1641,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B57" t="n">
@@ -1654,11 +1666,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B58" t="n">
-        <v>21.71262550354004</v>
+        <v>21.71262359619141</v>
       </c>
       <c r="C58" t="n">
         <v>23.65099906921387</v>
@@ -1679,11 +1691,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B59" t="n">
-        <v>22.08442878723145</v>
+        <v>22.08443260192871</v>
       </c>
       <c r="C59" t="n">
         <v>24.05599975585938</v>
@@ -1708,11 +1720,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B60" t="n">
-        <v>23.10896873474121</v>
+        <v>23.10897064208984</v>
       </c>
       <c r="C60" t="n">
         <v>25.17200088500977</v>
@@ -1737,7 +1749,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B61" t="n">
@@ -1766,7 +1778,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B62" t="n">
@@ -1795,11 +1807,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B63" t="n">
-        <v>27.68008995056152</v>
+        <v>27.68008804321289</v>
       </c>
       <c r="C63" t="n">
         <v>30.13400077819824</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B64" t="n">
-        <v>27.86876487731934</v>
+        <v>27.86876106262207</v>
       </c>
       <c r="C64" t="n">
         <v>30.32500076293945</v>
@@ -1853,7 +1865,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B65" t="n">
@@ -1882,11 +1894,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B66" t="n">
-        <v>29.14709663391113</v>
+        <v>29.14709281921387</v>
       </c>
       <c r="C66" t="n">
         <v>31.71599960327148</v>
@@ -1911,7 +1923,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B67" t="n">
@@ -1940,11 +1952,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B68" t="n">
-        <v>34.43803787231445</v>
+        <v>34.43804550170898</v>
       </c>
       <c r="C68" t="n">
         <v>37.45500183105469</v>
@@ -1969,7 +1981,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B69" t="n">
@@ -1998,11 +2010,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B70" t="n">
-        <v>32.70670318603516</v>
+        <v>32.70669937133789</v>
       </c>
       <c r="C70" t="n">
         <v>35.55699920654297</v>
@@ -2027,11 +2039,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B71" t="n">
-        <v>38.63322448730469</v>
+        <v>38.63321304321289</v>
       </c>
       <c r="C71" t="n">
         <v>42</v>
@@ -2056,11 +2068,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B72" t="n">
-        <v>38.68288040161133</v>
+        <v>38.68289184570312</v>
       </c>
       <c r="C72" t="n">
         <v>42.05400085449219</v>
@@ -2085,11 +2097,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B73" t="n">
-        <v>41.63004302978516</v>
+        <v>41.63006210327148</v>
       </c>
       <c r="C73" t="n">
         <v>45.22700119018555</v>
@@ -2114,11 +2126,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B74" t="n">
-        <v>37.4179801940918</v>
+        <v>37.41798400878906</v>
       </c>
       <c r="C74" t="n">
         <v>40.6510009765625</v>
@@ -2143,11 +2155,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B75" t="n">
-        <v>39.59029388427734</v>
+        <v>39.59029006958008</v>
       </c>
       <c r="C75" t="n">
         <v>43.01100158691406</v>
@@ -2172,11 +2184,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B76" t="n">
-        <v>40.21223449707031</v>
+        <v>40.21221923828125</v>
       </c>
       <c r="C76" t="n">
         <v>43.65700149536133</v>
@@ -2201,11 +2213,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B77" t="n">
-        <v>38.95309066772461</v>
+        <v>38.95308303833008</v>
       </c>
       <c r="C77" t="n">
         <v>42.29000091552734</v>
@@ -2230,11 +2242,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B78" t="n">
-        <v>41.58557510375977</v>
+        <v>41.58556747436523</v>
       </c>
       <c r="C78" t="n">
         <v>45.14799880981445</v>
@@ -2259,7 +2271,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B79" t="n">
@@ -2288,11 +2300,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B80" t="n">
-        <v>45.04050445556641</v>
+        <v>45.04050064086914</v>
       </c>
       <c r="C80" t="n">
         <v>48.86800003051758</v>
@@ -2317,11 +2329,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B81" t="n">
-        <v>45.28013610839844</v>
+        <v>45.28013229370117</v>
       </c>
       <c r="C81" t="n">
         <v>49.12799835205078</v>
@@ -2346,11 +2358,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B82" t="n">
-        <v>47.80778884887695</v>
+        <v>47.80778121948242</v>
       </c>
       <c r="C82" t="n">
         <v>51.84000015258789</v>
@@ -2375,11 +2387,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B83" t="n">
-        <v>47.75429153442383</v>
+        <v>47.75430297851562</v>
       </c>
       <c r="C83" t="n">
         <v>51.78200149536133</v>
@@ -2404,7 +2416,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B84" t="n">
@@ -2433,11 +2445,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B85" t="n">
-        <v>51.04954528808594</v>
+        <v>51.0495491027832</v>
       </c>
       <c r="C85" t="n">
         <v>55.29299926757812</v>
@@ -2462,11 +2474,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B86" t="n">
-        <v>52.64861297607422</v>
+        <v>52.64862442016602</v>
       </c>
       <c r="C86" t="n">
         <v>57.02500152587891</v>
@@ -2491,11 +2503,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B87" t="n">
-        <v>53.04099655151367</v>
+        <v>53.0410041809082</v>
       </c>
       <c r="C87" t="n">
         <v>57.45000076293945</v>
@@ -2520,11 +2532,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B88" t="n">
-        <v>56.43263626098633</v>
+        <v>56.43264007568359</v>
       </c>
       <c r="C88" t="n">
         <v>61.06100082397461</v>
@@ -2549,11 +2561,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B89" t="n">
-        <v>56.01396942138672</v>
+        <v>56.01397323608398</v>
       </c>
       <c r="C89" t="n">
         <v>60.60800170898438</v>
@@ -2578,11 +2590,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B90" t="n">
-        <v>62.17841720581055</v>
+        <v>62.17838668823242</v>
       </c>
       <c r="C90" t="n">
         <v>67.27799987792969</v>
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B91" t="n">
-        <v>66.33359527587891</v>
+        <v>66.33354949951172</v>
       </c>
       <c r="C91" t="n">
         <v>71.70999908447266</v>
@@ -2636,11 +2648,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B92" t="n">
-        <v>70.37683868408203</v>
+        <v>70.37685394287109</v>
       </c>
       <c r="C92" t="n">
         <v>76.08100128173828</v>
@@ -2665,7 +2677,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B93" t="n">
@@ -2694,11 +2706,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B94" t="n">
-        <v>70.09916687011719</v>
+        <v>70.09921264648438</v>
       </c>
       <c r="C94" t="n">
         <v>75.68000030517578</v>
@@ -2723,11 +2735,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B95" t="n">
-        <v>71.98878479003906</v>
+        <v>71.98876953125</v>
       </c>
       <c r="C95" t="n">
         <v>77.72000122070312</v>
@@ -2752,11 +2764,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B96" t="n">
-        <v>69.19147491455078</v>
+        <v>69.19145202636719</v>
       </c>
       <c r="C96" t="n">
         <v>74.69999694824219</v>
@@ -2781,11 +2793,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B97" t="n">
-        <v>68.230224609375</v>
+        <v>68.23023986816406</v>
       </c>
       <c r="C97" t="n">
         <v>73.55000305175781</v>
@@ -2810,11 +2822,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B98" t="n">
-        <v>70.92050933837891</v>
+        <v>70.92048645019531</v>
       </c>
       <c r="C98" t="n">
         <v>76.44999694824219</v>
@@ -2839,11 +2851,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B99" t="n">
-        <v>68.15602874755859</v>
+        <v>68.15605163574219</v>
       </c>
       <c r="C99" t="n">
         <v>73.47000122070312</v>
@@ -2868,11 +2880,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B100" t="n">
-        <v>68.88561248779297</v>
+        <v>68.88558959960938</v>
       </c>
       <c r="C100" t="n">
         <v>74.15000152587891</v>
@@ -2897,11 +2909,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B101" t="n">
-        <v>70.42775726318359</v>
+        <v>70.427734375</v>
       </c>
       <c r="C101" t="n">
         <v>75.80999755859375</v>
@@ -2926,11 +2938,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B102" t="n">
-        <v>68.67189788818359</v>
+        <v>68.67190551757812</v>
       </c>
       <c r="C102" t="n">
         <v>73.91999816894531</v>
@@ -2955,11 +2967,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B103" t="n">
-        <v>77.91902923583984</v>
+        <v>77.91904449462891</v>
       </c>
       <c r="C103" t="n">
         <v>83.75</v>
@@ -2984,11 +2996,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B104" t="n">
-        <v>81.21259307861328</v>
+        <v>81.21262359619141</v>
       </c>
       <c r="C104" t="n">
         <v>87.29000091552734</v>
@@ -3013,11 +3025,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B105" t="n">
-        <v>80.16128540039062</v>
+        <v>80.16129302978516</v>
       </c>
       <c r="C105" t="n">
         <v>86.16000366210938</v>
@@ -3042,7 +3054,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B106" t="n">
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B107" t="n">
-        <v>84.01665496826172</v>
+        <v>84.01663208007812</v>
       </c>
       <c r="C107" t="n">
         <v>90.12999725341797</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B108" t="n">
-        <v>80.53031921386719</v>
+        <v>80.53033447265625</v>
       </c>
       <c r="C108" t="n">
         <v>86.38999938964844</v>
@@ -3129,7 +3141,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B109" t="n">
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B110" t="n">
-        <v>86.16000366210938</v>
+        <v>86.16001892089844</v>
       </c>
       <c r="C110" t="n">
         <v>92.26000213623047</v>
@@ -3187,11 +3199,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B111" t="n">
-        <v>87.29933929443359</v>
+        <v>87.29934692382812</v>
       </c>
       <c r="C111" t="n">
         <v>93.48000335693359</v>
@@ -3216,7 +3228,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B112" t="n">
@@ -3245,11 +3257,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B113" t="n">
-        <v>86.40900421142578</v>
+        <v>86.40901184082031</v>
       </c>
       <c r="C113" t="n">
         <v>92.37000274658203</v>
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B114" t="n">
-        <v>84.30420684814453</v>
+        <v>84.30419921875</v>
       </c>
       <c r="C114" t="n">
         <v>90.12000274658203</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B115" t="n">
-        <v>92.75979614257812</v>
+        <v>92.75981903076172</v>
       </c>
       <c r="C115" t="n">
         <v>98.98999786376953</v>
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B116" t="n">
-        <v>91.75717163085938</v>
+        <v>91.75714111328125</v>
       </c>
       <c r="C116" t="n">
         <v>97.91999816894531</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B117" t="n">
-        <v>91.23239898681641</v>
+        <v>91.23241424560547</v>
       </c>
       <c r="C117" t="n">
         <v>97.36000061035156</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B118" t="n">
-        <v>83.59388732910156</v>
+        <v>83.5938720703125</v>
       </c>
       <c r="C118" t="n">
         <v>89.02999877929688</v>
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B119" t="n">
-        <v>81.61270141601562</v>
+        <v>81.61273956298828</v>
       </c>
       <c r="C119" t="n">
         <v>86.91999816894531</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B120" t="n">
-        <v>88.72988891601562</v>
+        <v>88.7298583984375</v>
       </c>
       <c r="C120" t="n">
         <v>94.5</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B121" t="n">
-        <v>91.25159454345703</v>
+        <v>91.2515869140625</v>
       </c>
       <c r="C121" t="n">
         <v>96.98999786376953</v>
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B122" t="n">
-        <v>90.22611999511719</v>
+        <v>90.22609710693359</v>
       </c>
       <c r="C122" t="n">
         <v>95.90000152587891</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B123" t="n">
-        <v>82.84995269775391</v>
+        <v>82.84993743896484</v>
       </c>
       <c r="C123" t="n">
         <v>88.05999755859375</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B124" t="n">
-        <v>89.79849243164062</v>
+        <v>89.79851531982422</v>
       </c>
       <c r="C124" t="n">
         <v>95.23999786376953</v>
@@ -3593,7 +3605,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B125" t="n">
@@ -3622,7 +3634,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B126" t="n">
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B127" t="n">
-        <v>101.0952301025391</v>
+        <v>101.0952224731445</v>
       </c>
       <c r="C127" t="n">
         <v>107.0199966430664</v>
@@ -3680,11 +3692,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B128" t="n">
-        <v>96.54206085205078</v>
+        <v>96.54207611083984</v>
       </c>
       <c r="C128" t="n">
         <v>102.1999969482422</v>
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B129" t="n">
-        <v>97.53390502929688</v>
+        <v>97.53392791748047</v>
       </c>
       <c r="C129" t="n">
         <v>103.25</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B130" t="n">
-        <v>100.6515731811523</v>
+        <v>100.6515655517578</v>
       </c>
       <c r="C130" t="n">
         <v>106.3300018310547</v>
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B131" t="n">
-        <v>104.5610046386719</v>
+        <v>104.5609970092773</v>
       </c>
       <c r="C131" t="n">
         <v>110.4599990844727</v>
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B132" t="n">
-        <v>106.4636535644531</v>
+        <v>106.4636611938477</v>
       </c>
       <c r="C132" t="n">
         <v>112.4700012207031</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B133" t="n">
-        <v>110.3246078491211</v>
+        <v>110.3245849609375</v>
       </c>
       <c r="C133" t="n">
         <v>116.3199996948242</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B134" t="n">
-        <v>116.5464782714844</v>
+        <v>116.5464553833008</v>
       </c>
       <c r="C134" t="n">
         <v>122.879997253418</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B135" t="n">
-        <v>115.1902008056641</v>
+        <v>115.1901931762695</v>
       </c>
       <c r="C135" t="n">
         <v>121.4499969482422</v>
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B136" t="n">
-        <v>121.4340744018555</v>
+        <v>121.43408203125</v>
       </c>
       <c r="C136" t="n">
         <v>127.8000030517578</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B137" t="n">
-        <v>126.6601257324219</v>
+        <v>126.6601104736328</v>
       </c>
       <c r="C137" t="n">
         <v>133.3000030517578</v>
@@ -3970,11 +3982,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B138" t="n">
-        <v>134.1666107177734</v>
+        <v>134.1666259765625</v>
       </c>
       <c r="C138" t="n">
         <v>141.1999969482422</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B139" t="n">
-        <v>141.5787200927734</v>
+        <v>141.5787811279297</v>
       </c>
       <c r="C139" t="n">
         <v>148.7700042724609</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B140" t="n">
-        <v>143.1965942382812</v>
+        <v>143.196533203125</v>
       </c>
       <c r="C140" t="n">
         <v>150.4700012207031</v>
@@ -4057,11 +4069,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B141" t="n">
-        <v>144.0435333251953</v>
+        <v>144.0435485839844</v>
       </c>
       <c r="C141" t="n">
         <v>151.3600006103516</v>
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B142" t="n">
-        <v>161.0840759277344</v>
+        <v>161.0840454101562</v>
       </c>
       <c r="C142" t="n">
         <v>169</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B143" t="n">
-        <v>167.5273742675781</v>
+        <v>167.5274047851562</v>
       </c>
       <c r="C143" t="n">
         <v>175.7599945068359</v>
@@ -4144,7 +4156,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B144" t="n">
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B145" t="n">
-        <v>170.1618499755859</v>
+        <v>170.1618347167969</v>
       </c>
       <c r="C145" t="n">
         <v>178.2700042724609</v>
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B146" t="n">
-        <v>181.4728698730469</v>
+        <v>181.4728546142578</v>
       </c>
       <c r="C146" t="n">
         <v>190.1199951171875</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B147" t="n">
-        <v>187.5817565917969</v>
+        <v>187.5817718505859</v>
       </c>
       <c r="C147" t="n">
         <v>196.5200042724609</v>
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B148" t="n">
-        <v>189.2323608398438</v>
+        <v>189.2323455810547</v>
       </c>
       <c r="C148" t="n">
         <v>198</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B149" t="n">
-        <v>206.0147552490234</v>
+        <v>206.0147705078125</v>
       </c>
       <c r="C149" t="n">
         <v>215.5599975585938</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B150" t="n">
-        <v>212.7526397705078</v>
+        <v>212.7525787353516</v>
       </c>
       <c r="C150" t="n">
         <v>222.6100006103516</v>
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B151" t="n">
-        <v>189.1356964111328</v>
+        <v>189.1357269287109</v>
       </c>
       <c r="C151" t="n">
         <v>197.6699981689453</v>
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B152" t="n">
-        <v>192.388916015625</v>
+        <v>192.3889617919922</v>
       </c>
       <c r="C152" t="n">
         <v>201.0700073242188</v>
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B153" t="n">
-        <v>180.5051879882812</v>
+        <v>180.5051727294922</v>
       </c>
       <c r="C153" t="n">
         <v>188.6499938964844</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B154" t="n">
-        <v>202.3638305664062</v>
+        <v>202.3638610839844</v>
       </c>
       <c r="C154" t="n">
         <v>211.1300048828125</v>
@@ -4463,7 +4475,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B155" t="n">
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B156" t="n">
-        <v>225.6740264892578</v>
+        <v>225.6740417480469</v>
       </c>
       <c r="C156" t="n">
         <v>235.4499969482422</v>
@@ -4521,7 +4533,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B157" t="n">
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B158" t="n">
-        <v>241.3847198486328</v>
+        <v>241.3846893310547</v>
       </c>
       <c r="C158" t="n">
         <v>251.4900054931641</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B159" t="n">
-        <v>253.9007720947266</v>
+        <v>253.9007415771484</v>
       </c>
       <c r="C159" t="n">
         <v>264.5299987792969</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B160" t="n">
-        <v>261.6470336914062</v>
+        <v>261.64697265625</v>
       </c>
       <c r="C160" t="n">
         <v>272.2699890136719</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B161" t="n">
-        <v>270.391845703125</v>
+        <v>270.3919372558594</v>
       </c>
       <c r="C161" t="n">
         <v>281.3699951171875</v>
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B162" t="n">
-        <v>260.9743041992188</v>
+        <v>260.9743957519531</v>
       </c>
       <c r="C162" t="n">
         <v>271.5700073242188</v>
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B163" t="n">
-        <v>266.332763671875</v>
+        <v>266.3326416015625</v>
       </c>
       <c r="C163" t="n">
         <v>276.8099975585938</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B164" t="n">
-        <v>281.1690979003906</v>
+        <v>281.169189453125</v>
       </c>
       <c r="C164" t="n">
         <v>292.2300109863281</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B165" t="n">
-        <v>287.2884216308594</v>
+        <v>287.2884521484375</v>
       </c>
       <c r="C165" t="n">
         <v>298.5899963378906</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B166" t="n">
-        <v>304.38720703125</v>
+        <v>304.3873291015625</v>
       </c>
       <c r="C166" t="n">
         <v>315.9400024414062</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B167" t="n">
-        <v>279.6366271972656</v>
+        <v>279.6365966796875</v>
       </c>
       <c r="C167" t="n">
         <v>290.25</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B168" t="n">
-        <v>232.7270660400391</v>
+        <v>232.7270812988281</v>
       </c>
       <c r="C168" t="n">
         <v>241.5599975585938</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B169" t="n">
-        <v>265.3250427246094</v>
+        <v>265.3250122070312</v>
       </c>
       <c r="C169" t="n">
         <v>274.9700012207031</v>
@@ -4898,7 +4910,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B170" t="n">
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B171" t="n">
-        <v>285.3279113769531</v>
+        <v>285.3279418945312</v>
       </c>
       <c r="C171" t="n">
         <v>295.7000122070312</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B172" t="n">
-        <v>298.1055297851562</v>
+        <v>298.10546875</v>
       </c>
       <c r="C172" t="n">
         <v>308.5299987792969</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B173" t="n">
-        <v>346.0876770019531</v>
+        <v>346.0875244140625</v>
       </c>
       <c r="C173" t="n">
         <v>358.1900024414062</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B174" t="n">
-        <v>326.743896484375</v>
+        <v>326.7439880371094</v>
       </c>
       <c r="C174" t="n">
         <v>338.1700134277344</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B175" t="n">
-        <v>279.2122802734375</v>
+        <v>279.2123413085938</v>
       </c>
       <c r="C175" t="n">
         <v>288.6400146484375</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B176" t="n">
-        <v>325.5187072753906</v>
+        <v>325.5187377929688</v>
       </c>
       <c r="C176" t="n">
         <v>336.510009765625</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B177" t="n">
-        <v>345.2814636230469</v>
+        <v>345.2814025878906</v>
       </c>
       <c r="C177" t="n">
         <v>356.9400024414062</v>
@@ -5130,7 +5142,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B178" t="n">
@@ -5159,7 +5171,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B179" t="n">
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B180" t="n">
-        <v>344.8570861816406</v>
+        <v>344.8570251464844</v>
       </c>
       <c r="C180" t="n">
         <v>356.0499877929688</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B181" t="n">
-        <v>370.4887390136719</v>
+        <v>370.4887084960938</v>
       </c>
       <c r="C181" t="n">
         <v>382.0599975585938</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B182" t="n">
-        <v>349.6591491699219</v>
+        <v>349.6593322753906</v>
       </c>
       <c r="C182" t="n">
         <v>360.5799865722656</v>
@@ -5275,7 +5287,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B183" t="n">
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B184" t="n">
-        <v>374.692138671875</v>
+        <v>374.6920471191406</v>
       </c>
       <c r="C184" t="n">
         <v>385.9400024414062</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B185" t="n">
-        <v>336.1393737792969</v>
+        <v>336.1394348144531</v>
       </c>
       <c r="C185" t="n">
         <v>346.2300109863281</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B186" t="n">
-        <v>337.5471496582031</v>
+        <v>337.5471801757812</v>
       </c>
       <c r="C186" t="n">
         <v>347.6799926757812</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B187" t="n">
-        <v>326.153076171875</v>
+        <v>326.1531066894531</v>
       </c>
       <c r="C187" t="n">
         <v>335.5199890136719</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B188" t="n">
-        <v>306.1282043457031</v>
+        <v>306.128173828125</v>
       </c>
       <c r="C188" t="n">
         <v>314.9200134277344</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B189" t="n">
-        <v>349.2886657714844</v>
+        <v>349.2886962890625</v>
       </c>
       <c r="C189" t="n">
         <v>359.3200073242188</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>376.0860595703125</v>
+        <v>376.0861206054688</v>
       </c>
       <c r="C190" t="n">
         <v>386.3800048828125</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B191" t="n">
-        <v>351.2070922851562</v>
+        <v>351.20703125</v>
       </c>
       <c r="C191" t="n">
         <v>360.8200073242188</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B192" t="n">
-        <v>347.8587036132812</v>
+        <v>347.8587341308594</v>
       </c>
       <c r="C192" t="n">
         <v>357.3800048828125</v>
@@ -5565,7 +5577,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B193" t="n">
@@ -5594,11 +5606,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B194" t="n">
-        <v>348.8190612792969</v>
+        <v>348.8190307617188</v>
       </c>
       <c r="C194" t="n">
         <v>357.8699951171875</v>
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B195" t="n">
-        <v>307.501220703125</v>
+        <v>307.5011596679688</v>
       </c>
       <c r="C195" t="n">
         <v>315.4800109863281</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B196" t="n">
-        <v>345.3707885742188</v>
+        <v>345.3708801269531</v>
       </c>
       <c r="C196" t="n">
         <v>353.7900085449219</v>
@@ -5681,7 +5693,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B197" t="n">
@@ -5710,7 +5722,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B198" t="n">
@@ -5739,7 +5751,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B199" t="n">
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B200" t="n">
-        <v>348.4800415039062</v>
+        <v>348.4800720214844</v>
       </c>
       <c r="C200" t="n">
         <v>356.3999938964844</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B201" t="n">
-        <v>340.0027160644531</v>
+        <v>340.0027465820312</v>
       </c>
       <c r="C201" t="n">
         <v>347.7300109863281</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B202" t="n">
-        <v>362.9526062011719</v>
+        <v>362.9525756835938</v>
       </c>
       <c r="C202" t="n">
         <v>370.6000061035156</v>
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B203" t="n">
-        <v>347.95849609375</v>
+        <v>347.9585571289062</v>
       </c>
       <c r="C203" t="n">
         <v>355.2900085449219</v>
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B204" t="n">
-        <v>355.9109802246094</v>
+        <v>355.9109191894531</v>
       </c>
       <c r="C204" t="n">
         <v>363.4100036621094</v>
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B205" t="n">
-        <v>372.7718505859375</v>
+        <v>372.7718811035156</v>
       </c>
       <c r="C205" t="n">
         <v>380.0299987792969</v>
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B206" t="n">
@@ -5971,11 +5983,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B207" t="n">
-        <v>385.7884826660156</v>
+        <v>385.7884216308594</v>
       </c>
       <c r="C207" t="n">
         <v>393.2999877929688</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B208" t="n">
-        <v>387.3090209960938</v>
+        <v>387.3090515136719</v>
       </c>
       <c r="C208" t="n">
         <v>394.2799987792969</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B209" t="n">
-        <v>405.3444213867188</v>
+        <v>405.3444519042969</v>
       </c>
       <c r="C209" t="n">
         <v>412.6400146484375</v>
@@ -6058,7 +6070,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B210" t="n">
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B211" t="n">
-        <v>370.23193359375</v>
+        <v>370.2319641113281</v>
       </c>
       <c r="C211" t="n">
         <v>376.3500061035156</v>
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B212" t="n">
-        <v>407.1026611328125</v>
+        <v>407.1026916503906</v>
       </c>
       <c r="C212" t="n">
         <v>413.8299865722656</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B213" t="n">
-        <v>419.5765686035156</v>
+        <v>419.5765991210938</v>
       </c>
       <c r="C213" t="n">
         <v>426.510009765625</v>
@@ -6174,7 +6186,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B214" t="n">
@@ -6203,11 +6215,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B215" t="n">
-        <v>467.7782592773438</v>
+        <v>467.7783508300781</v>
       </c>
       <c r="C215" t="n">
         <v>474.760009765625</v>
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B216" t="n">
-        <v>474.4881286621094</v>
+        <v>474.4881591796875</v>
       </c>
       <c r="C216" t="n">
         <v>481.5700073242188</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B217" t="n">
-        <v>445.1805725097656</v>
+        <v>445.1805419921875</v>
       </c>
       <c r="C217" t="n">
         <v>451.2000122070312</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B218" t="n">
-        <v>441.1056213378906</v>
+        <v>441.1056518554688</v>
       </c>
       <c r="C218" t="n">
         <v>447.0700073242188</v>
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B219" t="n">
-        <v>435.2745361328125</v>
+        <v>435.2744750976562</v>
       </c>
       <c r="C219" t="n">
         <v>441.1600036621094</v>
@@ -6348,7 +6360,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B220" t="n">
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B221" t="n">
-        <v>477.5980834960938</v>
+        <v>477.5981140136719</v>
       </c>
       <c r="C221" t="n">
         <v>483.3399963378906</v>
@@ -6406,7 +6418,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B222" t="n">
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B223" t="n">
-        <v>494.3114013671875</v>
+        <v>494.3114318847656</v>
       </c>
       <c r="C223" t="n">
         <v>499.5899963378906</v>
@@ -6464,11 +6476,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B224" t="n">
-        <v>527.3089599609375</v>
+        <v>527.3091430664062</v>
       </c>
       <c r="C224" t="n">
         <v>532.9400024414062</v>
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B225" t="n">
-        <v>521.0064697265625</v>
+        <v>521.0064086914062</v>
       </c>
       <c r="C225" t="n">
         <v>526.5700073242188</v>
@@ -6522,7 +6534,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B226" t="n">
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B227" t="n">
-        <v>571.061279296875</v>
+        <v>571.0612182617188</v>
       </c>
       <c r="C227" t="n">
         <v>576.3099975585938</v>
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B228" t="n">
-        <v>543.1279907226562</v>
+        <v>543.1280517578125</v>
       </c>
       <c r="C228" t="n">
         <v>548.1199951171875</v>
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B229" t="n">
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B230" t="n">
-        <v>581.18701171875</v>
+        <v>581.1869506835938</v>
       </c>
       <c r="C230" t="n">
         <v>585.5999755859375</v>
@@ -6667,7 +6679,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B231" t="n">
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B232" t="n">
-        <v>562.9617919921875</v>
+        <v>562.9618530273438</v>
       </c>
       <c r="C232" t="n">
         <v>566.469970703125</v>
@@ -6725,7 +6737,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B233" t="n">
@@ -6754,7 +6766,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B234" t="n">
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B235" t="n">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B236" t="n">
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B237" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B238" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B239" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B240" t="n">
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B241" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B242" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B243" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B244" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B245" t="n">
@@ -7102,32 +7114,32 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B246" t="n">
-        <v>559.9199829101562</v>
+        <v>566.0800170898438</v>
       </c>
       <c r="C246" t="n">
-        <v>559.9199829101562</v>
+        <v>566.0800170898438</v>
       </c>
       <c r="D246" t="n">
-        <v>41870100</v>
+        <v>44035500</v>
       </c>
       <c r="E246" t="n">
         <v>18.18</v>
       </c>
       <c r="F246" t="n">
-        <v>30.79867892795139</v>
+        <v>31.13751469141055</v>
       </c>
       <c r="G246" t="n">
         <v>882000000</v>
       </c>
       <c r="H246" t="n">
-        <v>493849424926.7578</v>
+        <v>499282575073.2422</v>
       </c>
       <c r="I246" t="n">
-        <v>0.04747176870748299</v>
+        <v>0.04992687074829932</v>
       </c>
     </row>
   </sheetData>
@@ -7159,75 +7171,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7263,13 +7275,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7431,13 +7443,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7464,7 +7476,7 @@
       <c r="I7" t="n">
         <v>1.116</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K7" t="n">
@@ -7477,13 +7489,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7510,7 +7522,7 @@
       <c r="I8" t="n">
         <v>1.182</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K8" t="n">
@@ -7523,13 +7535,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7556,7 +7568,7 @@
       <c r="I9" t="n">
         <v>1.264</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7569,13 +7581,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7602,7 +7614,7 @@
       <c r="I10" t="n">
         <v>1.313</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7615,13 +7627,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7648,7 +7660,7 @@
       <c r="I11" t="n">
         <v>1.405</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K11" t="n">
@@ -7661,13 +7673,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7694,7 +7706,7 @@
       <c r="I12" t="n">
         <v>1.488</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="K12" t="n">
@@ -7707,13 +7719,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7740,7 +7752,7 @@
       <c r="I13" t="n">
         <v>1.615</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="K13" t="n">
@@ -7753,13 +7765,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7786,7 +7798,7 @@
       <c r="I14" t="n">
         <v>1.784</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7799,13 +7811,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7832,7 +7844,7 @@
       <c r="I15" t="n">
         <v>1.483</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K15" t="n">
@@ -7845,13 +7857,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7878,7 +7890,7 @@
       <c r="I16" t="n">
         <v>1.59</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7891,13 +7903,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7924,7 +7936,7 @@
       <c r="I17" t="n">
         <v>1.669</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K17" t="n">
@@ -7937,13 +7949,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7970,7 +7982,7 @@
       <c r="I18" t="n">
         <v>1.723</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K18" t="n">
@@ -7983,13 +7995,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8016,7 +8028,7 @@
       <c r="I19" t="n">
         <v>2.194</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="K19" t="n">
@@ -8029,13 +8041,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8062,7 +8074,7 @@
       <c r="I20" t="n">
         <v>2.281</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8075,13 +8087,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8108,7 +8120,7 @@
       <c r="I21" t="n">
         <v>2.422</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8121,13 +8133,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8154,7 +8166,7 @@
       <c r="I22" t="n">
         <v>2.532</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K22" t="n">
@@ -8167,13 +8179,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8200,7 +8212,7 @@
       <c r="I23" t="n">
         <v>2.566</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K23" t="n">
@@ -8213,13 +8225,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8246,7 +8258,7 @@
       <c r="I24" t="n">
         <v>2.673</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K24" t="n">
@@ -8259,13 +8271,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8292,7 +8304,7 @@
       <c r="I25" t="n">
         <v>2.777</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -8305,13 +8317,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8338,7 +8350,7 @@
       <c r="I26" t="n">
         <v>2.92</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K26" t="n">
@@ -8351,13 +8363,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8384,7 +8396,7 @@
       <c r="I27" t="n">
         <v>3.09</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K27" t="n">
@@ -8397,13 +8409,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8430,7 +8442,7 @@
       <c r="I28" t="n">
         <v>3.25</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K28" t="n">
@@ -8443,13 +8455,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8476,7 +8488,7 @@
       <c r="I29" t="n">
         <v>3.26</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K29" t="n">
@@ -8489,13 +8501,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8522,7 +8534,7 @@
       <c r="I30" t="n">
         <v>3.25</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K30" t="n">
@@ -8535,13 +8547,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8568,7 +8580,7 @@
       <c r="I31" t="n">
         <v>3.350000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="K31" t="n">
@@ -8581,13 +8593,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8614,7 +8626,7 @@
       <c r="I32" t="n">
         <v>3.32</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K32" t="n">
@@ -8627,13 +8639,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8660,7 +8672,7 @@
       <c r="I33" t="n">
         <v>3.4</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K33" t="n">
@@ -8673,13 +8685,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8706,7 +8718,7 @@
       <c r="I34" t="n">
         <v>3.62</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K34" t="n">
@@ -8719,13 +8731,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8752,7 +8764,7 @@
       <c r="I35" t="n">
         <v>3.69</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="K35" t="n">
@@ -8765,13 +8777,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8798,7 +8810,7 @@
       <c r="I36" t="n">
         <v>3.83</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K36" t="n">
@@ -8811,13 +8823,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8844,7 +8856,7 @@
       <c r="I37" t="n">
         <v>4.040000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8857,13 +8869,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8890,7 +8902,7 @@
       <c r="I38" t="n">
         <v>4.300000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K38" t="n">
@@ -8903,13 +8915,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8936,7 +8948,7 @@
       <c r="I39" t="n">
         <v>3.65</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="K39" t="n">
@@ -8949,13 +8961,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8982,7 +8994,7 @@
       <c r="I40" t="n">
         <v>4.06</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -8995,13 +9007,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9028,7 +9040,7 @@
       <c r="I41" t="n">
         <v>4.46</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9041,13 +9053,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9074,7 +9086,7 @@
       <c r="I42" t="n">
         <v>4.94</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K42" t="n">
@@ -9087,13 +9099,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9120,7 +9132,7 @@
       <c r="I43" t="n">
         <v>5.600000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K43" t="n">
@@ -9133,13 +9145,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9166,7 +9178,7 @@
       <c r="I44" t="n">
         <v>5.99</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K44" t="n">
@@ -9179,13 +9191,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9212,7 +9224,7 @@
       <c r="I45" t="n">
         <v>6.49</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K45" t="n">
@@ -9225,13 +9237,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9258,7 +9270,7 @@
       <c r="I46" t="n">
         <v>6.74</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K46" t="n">
@@ -9271,13 +9283,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9304,7 +9316,7 @@
       <c r="I47" t="n">
         <v>7.94</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K47" t="n">
@@ -9317,13 +9329,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9350,7 +9362,7 @@
       <c r="I48" t="n">
         <v>7.819999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9363,13 +9375,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9396,7 +9408,7 @@
       <c r="I49" t="n">
         <v>7.23</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K49" t="n">
@@ -9409,13 +9421,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9442,7 +9454,7 @@
       <c r="I50" t="n">
         <v>6.67</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9455,13 +9467,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9488,7 +9500,7 @@
       <c r="I51" t="n">
         <v>6.37</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K51" t="n">
@@ -9501,13 +9513,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9534,7 +9546,7 @@
       <c r="I52" t="n">
         <v>6.52</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9547,13 +9559,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9580,7 +9592,7 @@
       <c r="I53" t="n">
         <v>7.19</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9593,13 +9605,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9626,7 +9638,7 @@
       <c r="I54" t="n">
         <v>8.120000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9639,13 +9651,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9672,7 +9684,7 @@
       <c r="I55" t="n">
         <v>8.76</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9685,13 +9697,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9718,7 +9730,7 @@
       <c r="I56" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9731,13 +9743,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9764,7 +9776,7 @@
       <c r="I57" t="n">
         <v>9.870000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9777,13 +9789,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9810,7 +9822,7 @@
       <c r="I58" t="n">
         <v>10.01</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9823,13 +9835,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9856,7 +9868,7 @@
       <c r="I59" t="n">
         <v>10.22</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K59" t="n">
@@ -9869,13 +9881,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9902,7 +9914,7 @@
       <c r="I60" t="n">
         <v>10.01</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9915,13 +9927,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9948,7 +9960,7 @@
       <c r="I61" t="n">
         <v>10.67</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9961,13 +9973,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9994,7 +10006,7 @@
       <c r="I62" t="n">
         <v>11.48</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10007,13 +10019,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10040,7 +10052,7 @@
       <c r="I63" t="n">
         <v>11.83</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="K63" t="n">
@@ -10053,13 +10065,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10086,7 +10098,7 @@
       <c r="I64" t="n">
         <v>12.58</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10099,13 +10111,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10132,7 +10144,7 @@
       <c r="I65" t="n">
         <v>13.08</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K65" t="n">
@@ -10145,13 +10157,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10178,7 +10190,7 @@
       <c r="I66" t="n">
         <v>13.22</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10191,13 +10203,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10224,7 +10236,7 @@
       <c r="I67" t="n">
         <v>13.89</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K67" t="n">
@@ -10237,13 +10249,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10270,7 +10282,7 @@
       <c r="I68" t="n">
         <v>14.26</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10283,13 +10295,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10316,7 +10328,7 @@
       <c r="I69" t="n">
         <v>14.83</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10329,13 +10341,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10362,7 +10374,7 @@
       <c r="I70" t="n">
         <v>15.64</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10375,13 +10387,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10408,7 +10420,7 @@
       <c r="I71" t="n">
         <v>16.52</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K71" t="n">
@@ -10421,13 +10433,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10454,7 +10466,7 @@
       <c r="I72" t="n">
         <v>17.28</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10467,13 +10479,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10500,7 +10512,7 @@
       <c r="I73" t="n">
         <v>18.18</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10538,57 +10550,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C2" t="n">
@@ -10622,10 +10634,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C3" t="n">
@@ -10659,10 +10671,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="C4" t="n">
@@ -10696,10 +10708,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="C5" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39447</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40227</v>
       </c>
       <c r="C6" t="n">
@@ -10770,10 +10782,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40227</v>
       </c>
       <c r="C7" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40227</v>
       </c>
       <c r="C8" t="n">
@@ -10844,10 +10856,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C9" t="n">
@@ -10881,10 +10893,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C10" t="n">
@@ -10918,10 +10930,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="C11" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C12" t="n">
@@ -10992,10 +11004,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C13" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C14" t="n">
@@ -11066,10 +11078,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C16" t="n">
@@ -11140,10 +11152,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="C17" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C18" t="n">
@@ -11214,10 +11226,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C19" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C20" t="n">
@@ -11288,10 +11300,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="C21" t="n">
@@ -11325,10 +11337,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C22" t="n">
@@ -11362,10 +11374,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C23" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C24" t="n">
@@ -11436,10 +11448,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C25" t="n">
@@ -11473,10 +11485,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C26" t="n">
@@ -11510,10 +11522,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C27" t="n">
@@ -11547,10 +11559,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C28" t="n">
@@ -11584,10 +11596,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C29" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C30" t="n">
@@ -11658,10 +11670,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C31" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C32" t="n">
@@ -11732,10 +11744,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="C33" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C34" t="n">
@@ -11806,10 +11818,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C35" t="n">
@@ -11843,10 +11855,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C36" t="n">
@@ -11880,10 +11892,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="C37" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C38" t="n">
@@ -11954,10 +11966,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C39" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C40" t="n">
@@ -12028,10 +12040,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43145</v>
       </c>
       <c r="C41" t="n">
@@ -12065,10 +12077,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C42" t="n">
@@ -12102,10 +12114,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C43" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C44" t="n">
@@ -12176,10 +12188,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C45" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C46" t="n">
@@ -12250,10 +12262,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C47" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C48" t="n">
@@ -12324,10 +12336,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C49" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C50" t="n">
@@ -12398,10 +12410,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C51" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C52" t="n">
@@ -12472,10 +12484,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C53" t="n">
@@ -12509,10 +12521,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C54" t="n">
@@ -12546,10 +12558,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C55" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C56" t="n">
@@ -12620,10 +12632,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C57" t="n">
@@ -12657,10 +12669,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C58" t="n">
@@ -12694,10 +12706,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C59" t="n">
@@ -12731,10 +12743,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C60" t="n">
@@ -12768,10 +12780,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C61" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C62" t="n">
@@ -12842,10 +12854,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C63" t="n">
@@ -12879,10 +12891,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C64" t="n">
@@ -12916,10 +12928,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="C65" t="n">
@@ -12953,10 +12965,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C66" t="n">
@@ -12990,10 +13002,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C67" t="n">
@@ -13027,10 +13039,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C68" t="n">
@@ -13064,10 +13076,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C69" t="n">
@@ -13101,10 +13113,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C70" t="n">
@@ -13138,10 +13150,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C71" t="n">
@@ -13175,10 +13187,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C72" t="n">
@@ -13212,10 +13224,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C73" t="n">
@@ -13249,10 +13261,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C74" t="n">
@@ -13286,10 +13298,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C75" t="n">
@@ -13341,12 +13353,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MA.xlsx
+++ b/salidas/empresas/MA.xlsx
@@ -498,7 +498,7 @@
         <v>38868</v>
       </c>
       <c r="B2" t="n">
-        <v>4.063895225524902</v>
+        <v>4.063896656036377</v>
       </c>
       <c r="C2" t="n">
         <v>4.49399995803833</v>
@@ -517,7 +517,7 @@
         <v>38898</v>
       </c>
       <c r="B3" t="n">
-        <v>4.340609550476074</v>
+        <v>4.340610504150391</v>
       </c>
       <c r="C3" t="n">
         <v>4.800000190734863</v>
@@ -536,7 +536,7 @@
         <v>38929</v>
       </c>
       <c r="B4" t="n">
-        <v>4.147995948791504</v>
+        <v>4.147997856140137</v>
       </c>
       <c r="C4" t="n">
         <v>4.586999893188477</v>
@@ -555,7 +555,7 @@
         <v>38960</v>
       </c>
       <c r="B5" t="n">
-        <v>5.055003643035889</v>
+        <v>5.055002212524414</v>
       </c>
       <c r="C5" t="n">
         <v>5.590000152587891</v>
@@ -574,7 +574,7 @@
         <v>38990</v>
       </c>
       <c r="B6" t="n">
-        <v>6.361708641052246</v>
+        <v>6.361708164215088</v>
       </c>
       <c r="C6" t="n">
         <v>7.034999847412109</v>
@@ -593,7 +593,7 @@
         <v>39021</v>
       </c>
       <c r="B7" t="n">
-        <v>6.709490299224854</v>
+        <v>6.70949125289917</v>
       </c>
       <c r="C7" t="n">
         <v>7.409999847412109</v>
@@ -612,7 +612,7 @@
         <v>39051</v>
       </c>
       <c r="B8" t="n">
-        <v>9.213101387023926</v>
+        <v>9.213099479675293</v>
       </c>
       <c r="C8" t="n">
         <v>10.17500019073486</v>
@@ -631,7 +631,7 @@
         <v>39082</v>
       </c>
       <c r="B9" t="n">
-        <v>8.917917251586914</v>
+        <v>8.917919158935547</v>
       </c>
       <c r="C9" t="n">
         <v>9.848999977111816</v>
@@ -650,7 +650,7 @@
         <v>39113</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10905838012695</v>
+        <v>10.10905933380127</v>
       </c>
       <c r="C10" t="n">
         <v>11.15499973297119</v>
@@ -669,7 +669,7 @@
         <v>39141</v>
       </c>
       <c r="B11" t="n">
-        <v>9.713035583496094</v>
+        <v>9.713032722473145</v>
       </c>
       <c r="C11" t="n">
         <v>10.7180004119873</v>
@@ -688,7 +688,7 @@
         <v>39172</v>
       </c>
       <c r="B12" t="n">
-        <v>9.627848625183105</v>
+        <v>9.627845764160156</v>
       </c>
       <c r="C12" t="n">
         <v>10.62399959564209</v>
@@ -707,7 +707,7 @@
         <v>39202</v>
       </c>
       <c r="B13" t="n">
-        <v>10.13484954833984</v>
+        <v>10.13485240936279</v>
       </c>
       <c r="C13" t="n">
         <v>11.16800022125244</v>
@@ -726,7 +726,7 @@
         <v>39233</v>
       </c>
       <c r="B14" t="n">
-        <v>13.57151317596436</v>
+        <v>13.57151222229004</v>
       </c>
       <c r="C14" t="n">
         <v>14.95499992370605</v>
@@ -745,7 +745,7 @@
         <v>39263</v>
       </c>
       <c r="B15" t="n">
-        <v>15.06625080108643</v>
+        <v>15.06624698638916</v>
       </c>
       <c r="C15" t="n">
         <v>16.58699989318848</v>
@@ -764,7 +764,7 @@
         <v>39294</v>
       </c>
       <c r="B16" t="n">
-        <v>14.60573387145996</v>
+        <v>14.60573959350586</v>
       </c>
       <c r="C16" t="n">
         <v>16.07999992370605</v>
@@ -783,7 +783,7 @@
         <v>39325</v>
       </c>
       <c r="B17" t="n">
-        <v>12.44303321838379</v>
+        <v>12.44302845001221</v>
       </c>
       <c r="C17" t="n">
         <v>13.69900035858154</v>
@@ -802,7 +802,7 @@
         <v>39355</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44036483764648</v>
+        <v>13.44036388397217</v>
       </c>
       <c r="C18" t="n">
         <v>14.79699993133545</v>
@@ -821,7 +821,7 @@
         <v>39386</v>
       </c>
       <c r="B19" t="n">
-        <v>17.26648902893066</v>
+        <v>17.26649284362793</v>
       </c>
       <c r="C19" t="n">
         <v>18.99099922180176</v>
@@ -840,7 +840,7 @@
         <v>39416</v>
       </c>
       <c r="B20" t="n">
-        <v>18.24296188354492</v>
+        <v>18.24296379089355</v>
       </c>
       <c r="C20" t="n">
         <v>20.06500053405762</v>
@@ -859,7 +859,7 @@
         <v>39447</v>
       </c>
       <c r="B21" t="n">
-        <v>19.56583786010742</v>
+        <v>19.56584167480469</v>
       </c>
       <c r="C21" t="n">
         <v>21.52000045776367</v>
@@ -878,7 +878,7 @@
         <v>39478</v>
       </c>
       <c r="B22" t="n">
-        <v>18.83456802368164</v>
+        <v>18.83457946777344</v>
       </c>
       <c r="C22" t="n">
         <v>20.70000076293945</v>
@@ -916,7 +916,7 @@
         <v>39538</v>
       </c>
       <c r="B24" t="n">
-        <v>20.28947067260742</v>
+        <v>20.28947830200195</v>
       </c>
       <c r="C24" t="n">
         <v>22.29899978637695</v>
@@ -935,7 +935,7 @@
         <v>39568</v>
       </c>
       <c r="B25" t="n">
-        <v>25.3260612487793</v>
+        <v>25.32606506347656</v>
       </c>
       <c r="C25" t="n">
         <v>27.81599998474121</v>
@@ -954,7 +954,7 @@
         <v>39599</v>
       </c>
       <c r="B26" t="n">
-        <v>28.10213088989258</v>
+        <v>28.10212135314941</v>
       </c>
       <c r="C26" t="n">
         <v>30.86499977111816</v>
@@ -973,7 +973,7 @@
         <v>39629</v>
       </c>
       <c r="B27" t="n">
-        <v>24.17520332336426</v>
+        <v>24.17521095275879</v>
       </c>
       <c r="C27" t="n">
         <v>26.55200004577637</v>
@@ -1011,7 +1011,7 @@
         <v>39691</v>
       </c>
       <c r="B29" t="n">
-        <v>22.09636878967285</v>
+        <v>22.09635543823242</v>
       </c>
       <c r="C29" t="n">
         <v>24.2549991607666</v>
@@ -1030,7 +1030,7 @@
         <v>39721</v>
       </c>
       <c r="B30" t="n">
-        <v>16.15480613708496</v>
+        <v>16.15480804443359</v>
       </c>
       <c r="C30" t="n">
         <v>17.73299980163574</v>
@@ -1049,7 +1049,7 @@
         <v>39752</v>
       </c>
       <c r="B31" t="n">
-        <v>13.47917556762695</v>
+        <v>13.4791784286499</v>
       </c>
       <c r="C31" t="n">
         <v>14.7819995880127</v>
@@ -1068,7 +1068,7 @@
         <v>39782</v>
       </c>
       <c r="B32" t="n">
-        <v>13.24938869476318</v>
+        <v>13.2493896484375</v>
       </c>
       <c r="C32" t="n">
         <v>14.52999973297119</v>
@@ -1087,7 +1087,7 @@
         <v>39813</v>
       </c>
       <c r="B33" t="n">
-        <v>13.03327560424805</v>
+        <v>13.03327751159668</v>
       </c>
       <c r="C33" t="n">
         <v>14.29300022125244</v>
@@ -1106,7 +1106,7 @@
         <v>39844</v>
       </c>
       <c r="B34" t="n">
-        <v>12.39276504516602</v>
+        <v>12.39277362823486</v>
       </c>
       <c r="C34" t="n">
         <v>13.57800006866455</v>
@@ -1125,7 +1125,7 @@
         <v>39872</v>
       </c>
       <c r="B35" t="n">
-        <v>14.42354869842529</v>
+        <v>14.42354488372803</v>
       </c>
       <c r="C35" t="n">
         <v>15.80300045013428</v>
@@ -1144,7 +1144,7 @@
         <v>39903</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28605175018311</v>
+        <v>15.28606224060059</v>
       </c>
       <c r="C36" t="n">
         <v>16.74799919128418</v>
@@ -1163,7 +1163,7 @@
         <v>39933</v>
       </c>
       <c r="B37" t="n">
-        <v>16.75881195068359</v>
+        <v>16.75881958007812</v>
       </c>
       <c r="C37" t="n">
         <v>18.34499931335449</v>
@@ -1182,7 +1182,7 @@
         <v>39964</v>
       </c>
       <c r="B38" t="n">
-        <v>16.10837554931641</v>
+        <v>16.1083812713623</v>
       </c>
       <c r="C38" t="n">
         <v>17.63299942016602</v>
@@ -1201,7 +1201,7 @@
         <v>39994</v>
       </c>
       <c r="B39" t="n">
-        <v>15.28437042236328</v>
+        <v>15.28436946868896</v>
       </c>
       <c r="C39" t="n">
         <v>16.73100090026855</v>
@@ -1220,7 +1220,7 @@
         <v>40025</v>
       </c>
       <c r="B40" t="n">
-        <v>17.74187088012695</v>
+        <v>17.74186706542969</v>
       </c>
       <c r="C40" t="n">
         <v>19.40299987792969</v>
@@ -1245,7 +1245,7 @@
         <v>40056</v>
       </c>
       <c r="B41" t="n">
-        <v>18.52824211120605</v>
+        <v>18.52824401855469</v>
       </c>
       <c r="C41" t="n">
         <v>20.26300048828125</v>
@@ -1270,7 +1270,7 @@
         <v>40086</v>
       </c>
       <c r="B42" t="n">
-        <v>18.4843578338623</v>
+        <v>18.48435020446777</v>
       </c>
       <c r="C42" t="n">
         <v>20.21500015258789</v>
@@ -1295,7 +1295,7 @@
         <v>40117</v>
       </c>
       <c r="B43" t="n">
-        <v>20.04189872741699</v>
+        <v>20.04190063476562</v>
       </c>
       <c r="C43" t="n">
         <v>21.90200042724609</v>
@@ -1320,7 +1320,7 @@
         <v>40147</v>
       </c>
       <c r="B44" t="n">
-        <v>22.04041290283203</v>
+        <v>22.04041862487793</v>
       </c>
       <c r="C44" t="n">
         <v>24.08600044250488</v>
@@ -1345,7 +1345,7 @@
         <v>40178</v>
       </c>
       <c r="B45" t="n">
-        <v>23.42401313781738</v>
+        <v>23.42400741577148</v>
       </c>
       <c r="C45" t="n">
         <v>25.59799957275391</v>
@@ -1370,7 +1370,7 @@
         <v>40209</v>
       </c>
       <c r="B46" t="n">
-        <v>22.88104438781738</v>
+        <v>22.88103675842285</v>
       </c>
       <c r="C46" t="n">
         <v>24.98999977111816</v>
@@ -1445,7 +1445,7 @@
         <v>40298</v>
       </c>
       <c r="B49" t="n">
-        <v>22.72391510009766</v>
+        <v>22.72390747070312</v>
       </c>
       <c r="C49" t="n">
         <v>24.80400085449219</v>
@@ -1470,7 +1470,7 @@
         <v>40329</v>
       </c>
       <c r="B50" t="n">
-        <v>18.48493766784668</v>
+        <v>18.48493385314941</v>
       </c>
       <c r="C50" t="n">
         <v>20.17700004577637</v>
@@ -1495,7 +1495,7 @@
         <v>40359</v>
       </c>
       <c r="B51" t="n">
-        <v>18.27973365783691</v>
+        <v>18.27972030639648</v>
       </c>
       <c r="C51" t="n">
         <v>19.95299911499023</v>
@@ -1520,7 +1520,7 @@
         <v>40390</v>
       </c>
       <c r="B52" t="n">
-        <v>19.25705909729004</v>
+        <v>19.25705718994141</v>
       </c>
       <c r="C52" t="n">
         <v>21.00399971008301</v>
@@ -1545,7 +1545,7 @@
         <v>40421</v>
       </c>
       <c r="B53" t="n">
-        <v>18.18620109558105</v>
+        <v>18.18620681762695</v>
       </c>
       <c r="C53" t="n">
         <v>19.83600044250488</v>
@@ -1570,7 +1570,7 @@
         <v>40451</v>
       </c>
       <c r="B54" t="n">
-        <v>20.53695297241211</v>
+        <v>20.53695487976074</v>
       </c>
       <c r="C54" t="n">
         <v>22.39999961853027</v>
@@ -1620,7 +1620,7 @@
         <v>40512</v>
       </c>
       <c r="B56" t="n">
-        <v>21.74618721008301</v>
+        <v>21.74619102478027</v>
       </c>
       <c r="C56" t="n">
         <v>23.70299911499023</v>
@@ -1645,7 +1645,7 @@
         <v>40543</v>
       </c>
       <c r="B57" t="n">
-        <v>20.56085014343262</v>
+        <v>20.56085968017578</v>
       </c>
       <c r="C57" t="n">
         <v>22.4109992980957</v>
@@ -1670,7 +1670,7 @@
         <v>40574</v>
       </c>
       <c r="B58" t="n">
-        <v>21.71262359619141</v>
+        <v>21.71261596679688</v>
       </c>
       <c r="C58" t="n">
         <v>23.65099906921387</v>
@@ -1695,7 +1695,7 @@
         <v>40602</v>
       </c>
       <c r="B59" t="n">
-        <v>22.08443260192871</v>
+        <v>22.08443450927734</v>
       </c>
       <c r="C59" t="n">
         <v>24.05599975585938</v>
@@ -1724,7 +1724,7 @@
         <v>40633</v>
       </c>
       <c r="B60" t="n">
-        <v>23.10897064208984</v>
+        <v>23.10896492004395</v>
       </c>
       <c r="C60" t="n">
         <v>25.17200088500977</v>
@@ -1753,7 +1753,7 @@
         <v>40663</v>
       </c>
       <c r="B61" t="n">
-        <v>25.34233283996582</v>
+        <v>25.34233665466309</v>
       </c>
       <c r="C61" t="n">
         <v>27.5890007019043</v>
@@ -1782,7 +1782,7 @@
         <v>40694</v>
       </c>
       <c r="B62" t="n">
-        <v>26.36745643615723</v>
+        <v>26.3674488067627</v>
       </c>
       <c r="C62" t="n">
         <v>28.70499992370605</v>
@@ -1811,7 +1811,7 @@
         <v>40724</v>
       </c>
       <c r="B63" t="n">
-        <v>27.68008804321289</v>
+        <v>27.68009185791016</v>
       </c>
       <c r="C63" t="n">
         <v>30.13400077819824</v>
@@ -1840,7 +1840,7 @@
         <v>40755</v>
       </c>
       <c r="B64" t="n">
-        <v>27.86876106262207</v>
+        <v>27.8687629699707</v>
       </c>
       <c r="C64" t="n">
         <v>30.32500076293945</v>
@@ -1869,7 +1869,7 @@
         <v>40786</v>
       </c>
       <c r="B65" t="n">
-        <v>30.30044174194336</v>
+        <v>30.30044555664062</v>
       </c>
       <c r="C65" t="n">
         <v>32.97100067138672</v>
@@ -1927,7 +1927,7 @@
         <v>40847</v>
       </c>
       <c r="B67" t="n">
-        <v>31.9270191192627</v>
+        <v>31.9270133972168</v>
       </c>
       <c r="C67" t="n">
         <v>34.7239990234375</v>
@@ -1956,7 +1956,7 @@
         <v>40877</v>
       </c>
       <c r="B68" t="n">
-        <v>34.43804550170898</v>
+        <v>34.43805694580078</v>
       </c>
       <c r="C68" t="n">
         <v>37.45500183105469</v>
@@ -1985,7 +1985,7 @@
         <v>40908</v>
       </c>
       <c r="B69" t="n">
-        <v>34.27898406982422</v>
+        <v>34.27898025512695</v>
       </c>
       <c r="C69" t="n">
         <v>37.28200149536133</v>
@@ -2014,7 +2014,7 @@
         <v>40939</v>
       </c>
       <c r="B70" t="n">
-        <v>32.70669937133789</v>
+        <v>32.70670700073242</v>
       </c>
       <c r="C70" t="n">
         <v>35.55699920654297</v>
@@ -2072,7 +2072,7 @@
         <v>40999</v>
       </c>
       <c r="B72" t="n">
-        <v>38.68289184570312</v>
+        <v>38.68289566040039</v>
       </c>
       <c r="C72" t="n">
         <v>42.05400085449219</v>
@@ -2101,7 +2101,7 @@
         <v>41029</v>
       </c>
       <c r="B73" t="n">
-        <v>41.63006210327148</v>
+        <v>41.63003540039062</v>
       </c>
       <c r="C73" t="n">
         <v>45.22700119018555</v>
@@ -2130,7 +2130,7 @@
         <v>41060</v>
       </c>
       <c r="B74" t="n">
-        <v>37.41798400878906</v>
+        <v>37.4179801940918</v>
       </c>
       <c r="C74" t="n">
         <v>40.6510009765625</v>
@@ -2188,7 +2188,7 @@
         <v>41121</v>
       </c>
       <c r="B76" t="n">
-        <v>40.21221923828125</v>
+        <v>40.21221160888672</v>
       </c>
       <c r="C76" t="n">
         <v>43.65700149536133</v>
@@ -2246,7 +2246,7 @@
         <v>41182</v>
       </c>
       <c r="B78" t="n">
-        <v>41.58556747436523</v>
+        <v>41.58556365966797</v>
       </c>
       <c r="C78" t="n">
         <v>45.14799880981445</v>
@@ -2275,7 +2275,7 @@
         <v>41213</v>
       </c>
       <c r="B79" t="n">
-        <v>42.48283386230469</v>
+        <v>42.48283767700195</v>
       </c>
       <c r="C79" t="n">
         <v>46.09299850463867</v>
@@ -2304,7 +2304,7 @@
         <v>41243</v>
       </c>
       <c r="B80" t="n">
-        <v>45.04050064086914</v>
+        <v>45.04048919677734</v>
       </c>
       <c r="C80" t="n">
         <v>48.86800003051758</v>
@@ -2333,7 +2333,7 @@
         <v>41274</v>
       </c>
       <c r="B81" t="n">
-        <v>45.28013229370117</v>
+        <v>45.28013610839844</v>
       </c>
       <c r="C81" t="n">
         <v>49.12799835205078</v>
@@ -2391,7 +2391,7 @@
         <v>41333</v>
       </c>
       <c r="B83" t="n">
-        <v>47.75430297851562</v>
+        <v>47.75430679321289</v>
       </c>
       <c r="C83" t="n">
         <v>51.78200149536133</v>
@@ -2420,7 +2420,7 @@
         <v>41364</v>
       </c>
       <c r="B84" t="n">
-        <v>49.90399169921875</v>
+        <v>49.90398025512695</v>
       </c>
       <c r="C84" t="n">
         <v>54.11299896240234</v>
@@ -2449,7 +2449,7 @@
         <v>41394</v>
       </c>
       <c r="B85" t="n">
-        <v>51.0495491027832</v>
+        <v>51.04953384399414</v>
       </c>
       <c r="C85" t="n">
         <v>55.29299926757812</v>
@@ -2507,7 +2507,7 @@
         <v>41455</v>
       </c>
       <c r="B87" t="n">
-        <v>53.0410041809082</v>
+        <v>53.04101181030273</v>
       </c>
       <c r="C87" t="n">
         <v>57.45000076293945</v>
@@ -2565,7 +2565,7 @@
         <v>41517</v>
       </c>
       <c r="B89" t="n">
-        <v>56.01397323608398</v>
+        <v>56.01397705078125</v>
       </c>
       <c r="C89" t="n">
         <v>60.60800170898438</v>
@@ -2594,7 +2594,7 @@
         <v>41547</v>
       </c>
       <c r="B90" t="n">
-        <v>62.17838668823242</v>
+        <v>62.17839431762695</v>
       </c>
       <c r="C90" t="n">
         <v>67.27799987792969</v>
@@ -2623,7 +2623,7 @@
         <v>41578</v>
       </c>
       <c r="B91" t="n">
-        <v>66.33354949951172</v>
+        <v>66.33357238769531</v>
       </c>
       <c r="C91" t="n">
         <v>71.70999908447266</v>
@@ -2652,7 +2652,7 @@
         <v>41608</v>
       </c>
       <c r="B92" t="n">
-        <v>70.37685394287109</v>
+        <v>70.37684631347656</v>
       </c>
       <c r="C92" t="n">
         <v>76.08100128173828</v>
@@ -2681,7 +2681,7 @@
         <v>41639</v>
       </c>
       <c r="B93" t="n">
-        <v>77.28216552734375</v>
+        <v>77.28215789794922</v>
       </c>
       <c r="C93" t="n">
         <v>83.54599761962891</v>
@@ -2710,7 +2710,7 @@
         <v>41670</v>
       </c>
       <c r="B94" t="n">
-        <v>70.09921264648438</v>
+        <v>70.09918212890625</v>
       </c>
       <c r="C94" t="n">
         <v>75.68000030517578</v>
@@ -2768,7 +2768,7 @@
         <v>41729</v>
       </c>
       <c r="B96" t="n">
-        <v>69.19145202636719</v>
+        <v>69.19148254394531</v>
       </c>
       <c r="C96" t="n">
         <v>74.69999694824219</v>
@@ -2826,7 +2826,7 @@
         <v>41790</v>
       </c>
       <c r="B98" t="n">
-        <v>70.92048645019531</v>
+        <v>70.92047119140625</v>
       </c>
       <c r="C98" t="n">
         <v>76.44999694824219</v>
@@ -2855,7 +2855,7 @@
         <v>41820</v>
       </c>
       <c r="B99" t="n">
-        <v>68.15605163574219</v>
+        <v>68.15601348876953</v>
       </c>
       <c r="C99" t="n">
         <v>73.47000122070312</v>
@@ -2913,7 +2913,7 @@
         <v>41882</v>
       </c>
       <c r="B101" t="n">
-        <v>70.427734375</v>
+        <v>70.42774963378906</v>
       </c>
       <c r="C101" t="n">
         <v>75.80999755859375</v>
@@ -2942,7 +2942,7 @@
         <v>41912</v>
       </c>
       <c r="B102" t="n">
-        <v>68.67190551757812</v>
+        <v>68.67192077636719</v>
       </c>
       <c r="C102" t="n">
         <v>73.91999816894531</v>
@@ -2971,7 +2971,7 @@
         <v>41943</v>
       </c>
       <c r="B103" t="n">
-        <v>77.91904449462891</v>
+        <v>77.91905212402344</v>
       </c>
       <c r="C103" t="n">
         <v>83.75</v>
@@ -3000,7 +3000,7 @@
         <v>41973</v>
       </c>
       <c r="B104" t="n">
-        <v>81.21262359619141</v>
+        <v>81.21257781982422</v>
       </c>
       <c r="C104" t="n">
         <v>87.29000091552734</v>
@@ -3029,7 +3029,7 @@
         <v>42004</v>
       </c>
       <c r="B105" t="n">
-        <v>80.16129302978516</v>
+        <v>80.16124725341797</v>
       </c>
       <c r="C105" t="n">
         <v>86.16000366210938</v>
@@ -3087,7 +3087,7 @@
         <v>42063</v>
       </c>
       <c r="B107" t="n">
-        <v>84.01663208007812</v>
+        <v>84.01666259765625</v>
       </c>
       <c r="C107" t="n">
         <v>90.12999725341797</v>
@@ -3116,7 +3116,7 @@
         <v>42094</v>
       </c>
       <c r="B108" t="n">
-        <v>80.53033447265625</v>
+        <v>80.53031921386719</v>
       </c>
       <c r="C108" t="n">
         <v>86.38999938964844</v>
@@ -3145,7 +3145,7 @@
         <v>42124</v>
       </c>
       <c r="B109" t="n">
-        <v>84.24553680419922</v>
+        <v>84.24555969238281</v>
       </c>
       <c r="C109" t="n">
         <v>90.20999908447266</v>
@@ -3203,7 +3203,7 @@
         <v>42185</v>
       </c>
       <c r="B111" t="n">
-        <v>87.29934692382812</v>
+        <v>87.29933929443359</v>
       </c>
       <c r="C111" t="n">
         <v>93.48000335693359</v>
@@ -3232,7 +3232,7 @@
         <v>42216</v>
       </c>
       <c r="B112" t="n">
-        <v>91.11439514160156</v>
+        <v>91.11441040039062</v>
       </c>
       <c r="C112" t="n">
         <v>97.40000152587891</v>
@@ -3261,7 +3261,7 @@
         <v>42247</v>
       </c>
       <c r="B113" t="n">
-        <v>86.40901184082031</v>
+        <v>86.40902709960938</v>
       </c>
       <c r="C113" t="n">
         <v>92.37000274658203</v>
@@ -3290,7 +3290,7 @@
         <v>42277</v>
       </c>
       <c r="B114" t="n">
-        <v>84.30419921875</v>
+        <v>84.30416107177734</v>
       </c>
       <c r="C114" t="n">
         <v>90.12000274658203</v>
@@ -3319,7 +3319,7 @@
         <v>42308</v>
       </c>
       <c r="B115" t="n">
-        <v>92.75981903076172</v>
+        <v>92.75980377197266</v>
       </c>
       <c r="C115" t="n">
         <v>98.98999786376953</v>
@@ -3348,7 +3348,7 @@
         <v>42338</v>
       </c>
       <c r="B116" t="n">
-        <v>91.75714111328125</v>
+        <v>91.75715637207031</v>
       </c>
       <c r="C116" t="n">
         <v>97.91999816894531</v>
@@ -3377,7 +3377,7 @@
         <v>42369</v>
       </c>
       <c r="B117" t="n">
-        <v>91.23241424560547</v>
+        <v>91.23239898681641</v>
       </c>
       <c r="C117" t="n">
         <v>97.36000061035156</v>
@@ -3435,7 +3435,7 @@
         <v>42429</v>
       </c>
       <c r="B119" t="n">
-        <v>81.61273956298828</v>
+        <v>81.61270141601562</v>
       </c>
       <c r="C119" t="n">
         <v>86.91999816894531</v>
@@ -3464,7 +3464,7 @@
         <v>42460</v>
       </c>
       <c r="B120" t="n">
-        <v>88.7298583984375</v>
+        <v>88.72986602783203</v>
       </c>
       <c r="C120" t="n">
         <v>94.5</v>
@@ -3493,7 +3493,7 @@
         <v>42490</v>
       </c>
       <c r="B121" t="n">
-        <v>91.2515869140625</v>
+        <v>91.25160217285156</v>
       </c>
       <c r="C121" t="n">
         <v>96.98999786376953</v>
@@ -3522,7 +3522,7 @@
         <v>42521</v>
       </c>
       <c r="B122" t="n">
-        <v>90.22609710693359</v>
+        <v>90.22608184814453</v>
       </c>
       <c r="C122" t="n">
         <v>95.90000152587891</v>
@@ -3580,7 +3580,7 @@
         <v>42582</v>
       </c>
       <c r="B124" t="n">
-        <v>89.79851531982422</v>
+        <v>89.79852294921875</v>
       </c>
       <c r="C124" t="n">
         <v>95.23999786376953</v>
@@ -3609,7 +3609,7 @@
         <v>42613</v>
       </c>
       <c r="B125" t="n">
-        <v>91.10907745361328</v>
+        <v>91.10906982421875</v>
       </c>
       <c r="C125" t="n">
         <v>96.62999725341797</v>
@@ -3667,7 +3667,7 @@
         <v>42674</v>
       </c>
       <c r="B127" t="n">
-        <v>101.0952224731445</v>
+        <v>101.0951995849609</v>
       </c>
       <c r="C127" t="n">
         <v>107.0199966430664</v>
@@ -3696,7 +3696,7 @@
         <v>42704</v>
       </c>
       <c r="B128" t="n">
-        <v>96.54207611083984</v>
+        <v>96.54206848144531</v>
       </c>
       <c r="C128" t="n">
         <v>102.1999969482422</v>
@@ -3725,7 +3725,7 @@
         <v>42735</v>
       </c>
       <c r="B129" t="n">
-        <v>97.53392791748047</v>
+        <v>97.533935546875</v>
       </c>
       <c r="C129" t="n">
         <v>103.25</v>
@@ -3754,7 +3754,7 @@
         <v>42766</v>
       </c>
       <c r="B130" t="n">
-        <v>100.6515655517578</v>
+        <v>100.6515502929688</v>
       </c>
       <c r="C130" t="n">
         <v>106.3300018310547</v>
@@ -3812,7 +3812,7 @@
         <v>42825</v>
       </c>
       <c r="B132" t="n">
-        <v>106.4636611938477</v>
+        <v>106.4636535644531</v>
       </c>
       <c r="C132" t="n">
         <v>112.4700012207031</v>
@@ -3841,7 +3841,7 @@
         <v>42855</v>
       </c>
       <c r="B133" t="n">
-        <v>110.3245849609375</v>
+        <v>110.324592590332</v>
       </c>
       <c r="C133" t="n">
         <v>116.3199996948242</v>
@@ -3870,7 +3870,7 @@
         <v>42886</v>
       </c>
       <c r="B134" t="n">
-        <v>116.5464553833008</v>
+        <v>116.5464706420898</v>
       </c>
       <c r="C134" t="n">
         <v>122.879997253418</v>
@@ -3899,7 +3899,7 @@
         <v>42916</v>
       </c>
       <c r="B135" t="n">
-        <v>115.1901931762695</v>
+        <v>115.190185546875</v>
       </c>
       <c r="C135" t="n">
         <v>121.4499969482422</v>
@@ -3928,7 +3928,7 @@
         <v>42947</v>
       </c>
       <c r="B136" t="n">
-        <v>121.43408203125</v>
+        <v>121.4340667724609</v>
       </c>
       <c r="C136" t="n">
         <v>127.8000030517578</v>
@@ -3957,7 +3957,7 @@
         <v>42978</v>
       </c>
       <c r="B137" t="n">
-        <v>126.6601104736328</v>
+        <v>126.6601181030273</v>
       </c>
       <c r="C137" t="n">
         <v>133.3000030517578</v>
@@ -3986,7 +3986,7 @@
         <v>43008</v>
       </c>
       <c r="B138" t="n">
-        <v>134.1666259765625</v>
+        <v>134.1665649414062</v>
       </c>
       <c r="C138" t="n">
         <v>141.1999969482422</v>
@@ -4044,7 +4044,7 @@
         <v>43069</v>
       </c>
       <c r="B140" t="n">
-        <v>143.196533203125</v>
+        <v>143.1965179443359</v>
       </c>
       <c r="C140" t="n">
         <v>150.4700012207031</v>
@@ -4073,7 +4073,7 @@
         <v>43100</v>
       </c>
       <c r="B141" t="n">
-        <v>144.0435485839844</v>
+        <v>144.0435333251953</v>
       </c>
       <c r="C141" t="n">
         <v>151.3600006103516</v>
@@ -4160,7 +4160,7 @@
         <v>43190</v>
       </c>
       <c r="B144" t="n">
-        <v>166.9555206298828</v>
+        <v>166.9555053710938</v>
       </c>
       <c r="C144" t="n">
         <v>175.1600036621094</v>
@@ -4189,7 +4189,7 @@
         <v>43220</v>
       </c>
       <c r="B145" t="n">
-        <v>170.1618347167969</v>
+        <v>170.1618804931641</v>
       </c>
       <c r="C145" t="n">
         <v>178.2700042724609</v>
@@ -4218,7 +4218,7 @@
         <v>43251</v>
       </c>
       <c r="B146" t="n">
-        <v>181.4728546142578</v>
+        <v>181.4729156494141</v>
       </c>
       <c r="C146" t="n">
         <v>190.1199951171875</v>
@@ -4247,7 +4247,7 @@
         <v>43281</v>
       </c>
       <c r="B147" t="n">
-        <v>187.5817718505859</v>
+        <v>187.581787109375</v>
       </c>
       <c r="C147" t="n">
         <v>196.5200042724609</v>
@@ -4305,7 +4305,7 @@
         <v>43343</v>
       </c>
       <c r="B149" t="n">
-        <v>206.0147705078125</v>
+        <v>206.0147552490234</v>
       </c>
       <c r="C149" t="n">
         <v>215.5599975585938</v>
@@ -4334,7 +4334,7 @@
         <v>43373</v>
       </c>
       <c r="B150" t="n">
-        <v>212.7525787353516</v>
+        <v>212.7526092529297</v>
       </c>
       <c r="C150" t="n">
         <v>222.6100006103516</v>
@@ -4421,7 +4421,7 @@
         <v>43465</v>
       </c>
       <c r="B153" t="n">
-        <v>180.5051727294922</v>
+        <v>180.5051422119141</v>
       </c>
       <c r="C153" t="n">
         <v>188.6499938964844</v>
@@ -4450,7 +4450,7 @@
         <v>43496</v>
       </c>
       <c r="B154" t="n">
-        <v>202.3638610839844</v>
+        <v>202.3638305664062</v>
       </c>
       <c r="C154" t="n">
         <v>211.1300048828125</v>
@@ -4479,7 +4479,7 @@
         <v>43524</v>
       </c>
       <c r="B155" t="n">
-        <v>215.4374847412109</v>
+        <v>215.4375610351562</v>
       </c>
       <c r="C155" t="n">
         <v>224.7700042724609</v>
@@ -4508,7 +4508,7 @@
         <v>43555</v>
       </c>
       <c r="B156" t="n">
-        <v>225.6740417480469</v>
+        <v>225.6740264892578</v>
       </c>
       <c r="C156" t="n">
         <v>235.4499969482422</v>
@@ -4566,7 +4566,7 @@
         <v>43616</v>
       </c>
       <c r="B158" t="n">
-        <v>241.3846893310547</v>
+        <v>241.3847198486328</v>
       </c>
       <c r="C158" t="n">
         <v>251.4900054931641</v>
@@ -4595,7 +4595,7 @@
         <v>43646</v>
       </c>
       <c r="B159" t="n">
-        <v>253.9007415771484</v>
+        <v>253.9007263183594</v>
       </c>
       <c r="C159" t="n">
         <v>264.5299987792969</v>
@@ -4624,7 +4624,7 @@
         <v>43677</v>
       </c>
       <c r="B160" t="n">
-        <v>261.64697265625</v>
+        <v>261.6470642089844</v>
       </c>
       <c r="C160" t="n">
         <v>272.2699890136719</v>
@@ -4653,7 +4653,7 @@
         <v>43708</v>
       </c>
       <c r="B161" t="n">
-        <v>270.3919372558594</v>
+        <v>270.3919982910156</v>
       </c>
       <c r="C161" t="n">
         <v>281.3699951171875</v>
@@ -4682,7 +4682,7 @@
         <v>43738</v>
       </c>
       <c r="B162" t="n">
-        <v>260.9743957519531</v>
+        <v>260.9743347167969</v>
       </c>
       <c r="C162" t="n">
         <v>271.5700073242188</v>
@@ -4711,7 +4711,7 @@
         <v>43769</v>
       </c>
       <c r="B163" t="n">
-        <v>266.3326416015625</v>
+        <v>266.3328552246094</v>
       </c>
       <c r="C163" t="n">
         <v>276.8099975585938</v>
@@ -4740,7 +4740,7 @@
         <v>43799</v>
       </c>
       <c r="B164" t="n">
-        <v>281.169189453125</v>
+        <v>281.1690979003906</v>
       </c>
       <c r="C164" t="n">
         <v>292.2300109863281</v>
@@ -4769,7 +4769,7 @@
         <v>43830</v>
       </c>
       <c r="B165" t="n">
-        <v>287.2884521484375</v>
+        <v>287.2883911132812</v>
       </c>
       <c r="C165" t="n">
         <v>298.5899963378906</v>
@@ -4798,7 +4798,7 @@
         <v>43861</v>
       </c>
       <c r="B166" t="n">
-        <v>304.3873291015625</v>
+        <v>304.3872680664062</v>
       </c>
       <c r="C166" t="n">
         <v>315.9400024414062</v>
@@ -4827,7 +4827,7 @@
         <v>43890</v>
       </c>
       <c r="B167" t="n">
-        <v>279.6365966796875</v>
+        <v>279.6366271972656</v>
       </c>
       <c r="C167" t="n">
         <v>290.25</v>
@@ -4856,7 +4856,7 @@
         <v>43921</v>
       </c>
       <c r="B168" t="n">
-        <v>232.7270812988281</v>
+        <v>232.7270965576172</v>
       </c>
       <c r="C168" t="n">
         <v>241.5599975585938</v>
@@ -4885,7 +4885,7 @@
         <v>43951</v>
       </c>
       <c r="B169" t="n">
-        <v>265.3250122070312</v>
+        <v>265.3250427246094</v>
       </c>
       <c r="C169" t="n">
         <v>274.9700012207031</v>
@@ -4914,7 +4914,7 @@
         <v>43982</v>
       </c>
       <c r="B170" t="n">
-        <v>290.3358764648438</v>
+        <v>290.3358459472656</v>
       </c>
       <c r="C170" t="n">
         <v>300.8900146484375</v>
@@ -4943,7 +4943,7 @@
         <v>44012</v>
       </c>
       <c r="B171" t="n">
-        <v>285.3279418945312</v>
+        <v>285.3279113769531</v>
       </c>
       <c r="C171" t="n">
         <v>295.7000122070312</v>
@@ -4972,7 +4972,7 @@
         <v>44043</v>
       </c>
       <c r="B172" t="n">
-        <v>298.10546875</v>
+        <v>298.1054077148438</v>
       </c>
       <c r="C172" t="n">
         <v>308.5299987792969</v>
@@ -5001,7 +5001,7 @@
         <v>44074</v>
       </c>
       <c r="B173" t="n">
-        <v>346.0875244140625</v>
+        <v>346.0875854492188</v>
       </c>
       <c r="C173" t="n">
         <v>358.1900024414062</v>
@@ -5030,7 +5030,7 @@
         <v>44104</v>
       </c>
       <c r="B174" t="n">
-        <v>326.7439880371094</v>
+        <v>326.7440490722656</v>
       </c>
       <c r="C174" t="n">
         <v>338.1700134277344</v>
@@ -5059,7 +5059,7 @@
         <v>44135</v>
       </c>
       <c r="B175" t="n">
-        <v>279.2123413085938</v>
+        <v>279.2122802734375</v>
       </c>
       <c r="C175" t="n">
         <v>288.6400146484375</v>
@@ -5117,7 +5117,7 @@
         <v>44196</v>
       </c>
       <c r="B177" t="n">
-        <v>345.2814025878906</v>
+        <v>345.2814331054688</v>
       </c>
       <c r="C177" t="n">
         <v>356.9400024414062</v>
@@ -5146,7 +5146,7 @@
         <v>44227</v>
       </c>
       <c r="B178" t="n">
-        <v>306.3469848632812</v>
+        <v>306.3469543457031</v>
       </c>
       <c r="C178" t="n">
         <v>316.2900085449219</v>
@@ -5175,7 +5175,7 @@
         <v>44255</v>
       </c>
       <c r="B179" t="n">
-        <v>342.7262573242188</v>
+        <v>342.7261962890625</v>
       </c>
       <c r="C179" t="n">
         <v>353.8500061035156</v>
@@ -5204,7 +5204,7 @@
         <v>44286</v>
       </c>
       <c r="B180" t="n">
-        <v>344.8570251464844</v>
+        <v>344.8570556640625</v>
       </c>
       <c r="C180" t="n">
         <v>356.0499877929688</v>
@@ -5233,7 +5233,7 @@
         <v>44316</v>
       </c>
       <c r="B181" t="n">
-        <v>370.4887084960938</v>
+        <v>370.4887390136719</v>
       </c>
       <c r="C181" t="n">
         <v>382.0599975585938</v>
@@ -5262,7 +5262,7 @@
         <v>44347</v>
       </c>
       <c r="B182" t="n">
-        <v>349.6593322753906</v>
+        <v>349.6592407226562</v>
       </c>
       <c r="C182" t="n">
         <v>360.5799865722656</v>
@@ -5291,7 +5291,7 @@
         <v>44377</v>
       </c>
       <c r="B183" t="n">
-        <v>354.0326843261719</v>
+        <v>354.0326538085938</v>
       </c>
       <c r="C183" t="n">
         <v>365.0899963378906</v>
@@ -5320,7 +5320,7 @@
         <v>44408</v>
       </c>
       <c r="B184" t="n">
-        <v>374.6920471191406</v>
+        <v>374.6920776367188</v>
       </c>
       <c r="C184" t="n">
         <v>385.9400024414062</v>
@@ -5349,7 +5349,7 @@
         <v>44439</v>
       </c>
       <c r="B185" t="n">
-        <v>336.1394348144531</v>
+        <v>336.139404296875</v>
       </c>
       <c r="C185" t="n">
         <v>346.2300109863281</v>
@@ -5378,7 +5378,7 @@
         <v>44469</v>
       </c>
       <c r="B186" t="n">
-        <v>337.5471801757812</v>
+        <v>337.5471496582031</v>
       </c>
       <c r="C186" t="n">
         <v>347.6799926757812</v>
@@ -5407,7 +5407,7 @@
         <v>44500</v>
       </c>
       <c r="B187" t="n">
-        <v>326.1531066894531</v>
+        <v>326.153076171875</v>
       </c>
       <c r="C187" t="n">
         <v>335.5199890136719</v>
@@ -5436,7 +5436,7 @@
         <v>44530</v>
       </c>
       <c r="B188" t="n">
-        <v>306.128173828125</v>
+        <v>306.1282043457031</v>
       </c>
       <c r="C188" t="n">
         <v>314.9200134277344</v>
@@ -5494,7 +5494,7 @@
         <v>44592</v>
       </c>
       <c r="B190" t="n">
-        <v>376.0861206054688</v>
+        <v>376.0860595703125</v>
       </c>
       <c r="C190" t="n">
         <v>386.3800048828125</v>
@@ -5523,7 +5523,7 @@
         <v>44620</v>
       </c>
       <c r="B191" t="n">
-        <v>351.20703125</v>
+        <v>351.2070922851562</v>
       </c>
       <c r="C191" t="n">
         <v>360.8200073242188</v>
@@ -5552,7 +5552,7 @@
         <v>44651</v>
       </c>
       <c r="B192" t="n">
-        <v>347.8587341308594</v>
+        <v>347.8587036132812</v>
       </c>
       <c r="C192" t="n">
         <v>357.3800048828125</v>
@@ -5581,7 +5581,7 @@
         <v>44681</v>
       </c>
       <c r="B193" t="n">
-        <v>354.1897583007812</v>
+        <v>354.189697265625</v>
       </c>
       <c r="C193" t="n">
         <v>363.3800048828125</v>
@@ -5639,7 +5639,7 @@
         <v>44742</v>
       </c>
       <c r="B195" t="n">
-        <v>307.5011596679688</v>
+        <v>307.5011901855469</v>
       </c>
       <c r="C195" t="n">
         <v>315.4800109863281</v>
@@ -5668,7 +5668,7 @@
         <v>44773</v>
       </c>
       <c r="B196" t="n">
-        <v>345.3708801269531</v>
+        <v>345.3708190917969</v>
       </c>
       <c r="C196" t="n">
         <v>353.7900085449219</v>
@@ -5755,7 +5755,7 @@
         <v>44865</v>
       </c>
       <c r="B199" t="n">
-        <v>320.8871765136719</v>
+        <v>320.8871459960938</v>
       </c>
       <c r="C199" t="n">
         <v>328.1799926757812</v>
@@ -5813,7 +5813,7 @@
         <v>44926</v>
       </c>
       <c r="B201" t="n">
-        <v>340.0027465820312</v>
+        <v>340.0027770996094</v>
       </c>
       <c r="C201" t="n">
         <v>347.7300109863281</v>
@@ -5842,7 +5842,7 @@
         <v>44957</v>
       </c>
       <c r="B202" t="n">
-        <v>362.9525756835938</v>
+        <v>362.9526062011719</v>
       </c>
       <c r="C202" t="n">
         <v>370.6000061035156</v>
@@ -5871,7 +5871,7 @@
         <v>44985</v>
       </c>
       <c r="B203" t="n">
-        <v>347.9585571289062</v>
+        <v>347.95849609375</v>
       </c>
       <c r="C203" t="n">
         <v>355.2900085449219</v>
@@ -5900,7 +5900,7 @@
         <v>45016</v>
       </c>
       <c r="B204" t="n">
-        <v>355.9109191894531</v>
+        <v>355.9109802246094</v>
       </c>
       <c r="C204" t="n">
         <v>363.4100036621094</v>
@@ -5929,7 +5929,7 @@
         <v>45046</v>
       </c>
       <c r="B205" t="n">
-        <v>372.7718811035156</v>
+        <v>372.7719116210938</v>
       </c>
       <c r="C205" t="n">
         <v>380.0299987792969</v>
@@ -5958,7 +5958,7 @@
         <v>45077</v>
       </c>
       <c r="B206" t="n">
-        <v>358.0485534667969</v>
+        <v>358.0485229492188</v>
       </c>
       <c r="C206" t="n">
         <v>365.0199890136719</v>
@@ -5987,7 +5987,7 @@
         <v>45107</v>
       </c>
       <c r="B207" t="n">
-        <v>385.7884216308594</v>
+        <v>385.7884826660156</v>
       </c>
       <c r="C207" t="n">
         <v>393.2999877929688</v>
@@ -6016,7 +6016,7 @@
         <v>45138</v>
       </c>
       <c r="B208" t="n">
-        <v>387.3090515136719</v>
+        <v>387.3090209960938</v>
       </c>
       <c r="C208" t="n">
         <v>394.2799987792969</v>
@@ -6045,7 +6045,7 @@
         <v>45169</v>
       </c>
       <c r="B209" t="n">
-        <v>405.3444519042969</v>
+        <v>405.3444213867188</v>
       </c>
       <c r="C209" t="n">
         <v>412.6400146484375</v>
@@ -6103,7 +6103,7 @@
         <v>45230</v>
       </c>
       <c r="B211" t="n">
-        <v>370.2319641113281</v>
+        <v>370.2319946289062</v>
       </c>
       <c r="C211" t="n">
         <v>376.3500061035156</v>
@@ -6132,7 +6132,7 @@
         <v>45260</v>
       </c>
       <c r="B212" t="n">
-        <v>407.1026916503906</v>
+        <v>407.1026306152344</v>
       </c>
       <c r="C212" t="n">
         <v>413.8299865722656</v>
@@ -6161,7 +6161,7 @@
         <v>45291</v>
       </c>
       <c r="B213" t="n">
-        <v>419.5765991210938</v>
+        <v>419.5765380859375</v>
       </c>
       <c r="C213" t="n">
         <v>426.510009765625</v>
@@ -6190,7 +6190,7 @@
         <v>45322</v>
       </c>
       <c r="B214" t="n">
-        <v>442.6237487792969</v>
+        <v>442.6237182617188</v>
       </c>
       <c r="C214" t="n">
         <v>449.2300109863281</v>
@@ -6219,7 +6219,7 @@
         <v>45351</v>
       </c>
       <c r="B215" t="n">
-        <v>467.7783508300781</v>
+        <v>467.7783203125</v>
       </c>
       <c r="C215" t="n">
         <v>474.760009765625</v>
@@ -6277,7 +6277,7 @@
         <v>45412</v>
       </c>
       <c r="B217" t="n">
-        <v>445.1805419921875</v>
+        <v>445.1805725097656</v>
       </c>
       <c r="C217" t="n">
         <v>451.2000122070312</v>
@@ -6306,7 +6306,7 @@
         <v>45443</v>
       </c>
       <c r="B218" t="n">
-        <v>441.1056518554688</v>
+        <v>441.1056823730469</v>
       </c>
       <c r="C218" t="n">
         <v>447.0700073242188</v>
@@ -6335,7 +6335,7 @@
         <v>45473</v>
       </c>
       <c r="B219" t="n">
-        <v>435.2744750976562</v>
+        <v>435.2745056152344</v>
       </c>
       <c r="C219" t="n">
         <v>441.1600036621094</v>
@@ -6393,7 +6393,7 @@
         <v>45535</v>
       </c>
       <c r="B221" t="n">
-        <v>477.5981140136719</v>
+        <v>477.59814453125</v>
       </c>
       <c r="C221" t="n">
         <v>483.3399963378906</v>
@@ -6451,7 +6451,7 @@
         <v>45596</v>
       </c>
       <c r="B223" t="n">
-        <v>494.3114318847656</v>
+        <v>494.3114624023438</v>
       </c>
       <c r="C223" t="n">
         <v>499.5899963378906</v>
@@ -6480,7 +6480,7 @@
         <v>45626</v>
       </c>
       <c r="B224" t="n">
-        <v>527.3091430664062</v>
+        <v>527.3090209960938</v>
       </c>
       <c r="C224" t="n">
         <v>532.9400024414062</v>
@@ -6567,7 +6567,7 @@
         <v>45716</v>
       </c>
       <c r="B227" t="n">
-        <v>571.0612182617188</v>
+        <v>571.0611572265625</v>
       </c>
       <c r="C227" t="n">
         <v>576.3099975585938</v>
@@ -6596,7 +6596,7 @@
         <v>45747</v>
       </c>
       <c r="B228" t="n">
-        <v>543.1280517578125</v>
+        <v>543.1279907226562</v>
       </c>
       <c r="C228" t="n">
         <v>548.1199951171875</v>
@@ -6625,7 +6625,7 @@
         <v>45777</v>
       </c>
       <c r="B229" t="n">
-        <v>543.929931640625</v>
+        <v>543.9299926757812</v>
       </c>
       <c r="C229" t="n">
         <v>548.0599975585938</v>
@@ -6654,7 +6654,7 @@
         <v>45808</v>
       </c>
       <c r="B230" t="n">
-        <v>581.1869506835938</v>
+        <v>581.18701171875</v>
       </c>
       <c r="C230" t="n">
         <v>585.5999755859375</v>
